--- a/data/raw_data/all_ingredients.xlsx
+++ b/data/raw_data/all_ingredients.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F2AD20-AC53-4A80-B6B7-ABF704C7ECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D46DAA-75DF-412C-B64D-BD2A3677E4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36" yWindow="0" windowWidth="23016" windowHeight="16656" xr2:uid="{EACE1C46-B374-4940-8FA1-58EDCA6D9B2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EACE1C46-B374-4940-8FA1-58EDCA6D9B2B}"/>
   </bookViews>
   <sheets>
     <sheet name="all_ingredients" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="trash fish table" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_ingredients!$A$1:$S$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all_ingredients!$A$1:$S$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sources!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="135">
   <si>
     <t>ingredient</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Shrimp meal | Feedipedia</t>
+  </si>
+  <si>
+    <t>corn-oil</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
@@ -1611,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="9">
-        <f t="shared" ref="J3:J61" si="0">SUM(F3:I3)</f>
+        <f>SUM(F3:I3)</f>
         <v>1</v>
       </c>
       <c r="K3" s="5">
@@ -1676,7 +1679,7 @@
         <v>0.13</v>
       </c>
       <c r="J4" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F4:I4)</f>
         <v>1</v>
       </c>
       <c r="K4" s="6">
@@ -1739,7 +1742,7 @@
         <v>7.6272807017543895E-2</v>
       </c>
       <c r="J5" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F5:I5)</f>
         <v>1</v>
       </c>
       <c r="K5" s="6">
@@ -1801,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F6:I6)</f>
         <v>1</v>
       </c>
       <c r="K6" s="5">
@@ -1859,7 +1862,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F7:I7)</f>
         <v>1</v>
       </c>
       <c r="K7" s="8">
@@ -1898,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F8:I8)</f>
         <v>1</v>
       </c>
       <c r="K8" s="8">
@@ -1958,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F9:I9)</f>
         <v>1</v>
       </c>
       <c r="K9" s="8">
@@ -2018,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F10:I10)</f>
         <v>1</v>
       </c>
       <c r="K10" s="9">
@@ -2075,7 +2078,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F11:I11)</f>
         <v>1</v>
       </c>
       <c r="K11" s="17">
@@ -2118,7 +2121,7 @@
         <v>0.02</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F12:I12)</f>
         <v>1</v>
       </c>
       <c r="K12" s="5">
@@ -2185,7 +2188,7 @@
         <v>0.02</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F13:I13)</f>
         <v>1</v>
       </c>
       <c r="K13" s="5">
@@ -2224,7 +2227,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
@@ -2233,70 +2236,70 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="11">
-        <v>0.84</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0.05</v>
-      </c>
-      <c r="H14" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0.04</v>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F14:I14)</f>
         <v>1</v>
       </c>
-      <c r="K14" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="L14" s="11">
-        <f>K14*0.94</f>
-        <v>0.82719999999999994</v>
-      </c>
-      <c r="M14" s="11">
-        <f>L14*1.06</f>
-        <v>0.87683199999999994</v>
-      </c>
-      <c r="N14" s="11">
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <f>K14*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <f>L14*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
         <v>0.95176181599999998</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="5">
         <f>N14*0.95</f>
         <v>0.90417372519999994</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="5">
         <f>N14*1.05</f>
         <v>0.99934990680000002</v>
       </c>
-      <c r="Q14" s="11">
-        <v>0.77</v>
-      </c>
-      <c r="R14" s="11">
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
         <f>Q14*0.95</f>
-        <v>0.73149999999999993</v>
-      </c>
-      <c r="S14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7">
         <f>R14*1.05</f>
-        <v>0.76807499999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>69</v>
@@ -2304,190 +2307,191 @@
       <c r="E15" t="s">
         <v>69</v>
       </c>
-      <c r="F15">
-        <v>0.3</v>
-      </c>
-      <c r="G15">
-        <v>0.02</v>
-      </c>
-      <c r="H15" s="7">
-        <f>1-SUM(F15:G15,I15)</f>
-        <v>0.64</v>
-      </c>
-      <c r="I15">
+      <c r="F15" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="H15" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I15" s="11">
         <v>0.04</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F15:I15)</f>
         <v>1</v>
       </c>
-      <c r="K15">
-        <v>0.86</v>
-      </c>
-      <c r="L15" s="4">
-        <f>K15*0.95</f>
-        <v>0.81699999999999995</v>
-      </c>
-      <c r="M15" s="4">
-        <f>L15*1.05</f>
-        <v>0.85785</v>
-      </c>
-      <c r="N15">
-        <v>0.93</v>
-      </c>
-      <c r="O15">
+      <c r="K15" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="L15" s="11">
+        <f>K15*0.94</f>
+        <v>0.82719999999999994</v>
+      </c>
+      <c r="M15" s="11">
+        <f>L15*1.06</f>
+        <v>0.87683199999999994</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O15" s="11">
         <f>N15*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P15">
-        <f>MIN(N15*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q15">
-        <v>0.6</v>
-      </c>
-      <c r="R15" s="4">
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P15" s="11">
+        <f>N15*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="R15" s="11">
         <f>Q15*0.95</f>
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="S15" s="4">
+        <v>0.73149999999999993</v>
+      </c>
+      <c r="S15" s="11">
         <f>R15*1.05</f>
-        <v>0.59849999999999992</v>
+        <v>0.76807499999999995</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16">
+        <v>0.3</v>
+      </c>
+      <c r="G16">
+        <v>0.02</v>
+      </c>
+      <c r="H16" s="7">
+        <f>1-SUM(F16:G16,I16)</f>
+        <v>0.64</v>
+      </c>
+      <c r="I16">
+        <v>0.04</v>
+      </c>
+      <c r="J16" s="9">
+        <f>SUM(F16:I16)</f>
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>0.86</v>
+      </c>
+      <c r="L16" s="4">
+        <f>K16*0.95</f>
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="M16" s="4">
+        <f>L16*1.05</f>
+        <v>0.85785</v>
+      </c>
+      <c r="N16">
+        <v>0.93</v>
+      </c>
+      <c r="O16">
+        <f>N16*0.95</f>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P16">
+        <f>MIN(N16*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q16">
+        <v>0.6</v>
+      </c>
+      <c r="R16" s="4">
+        <f>Q16*0.95</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="S16" s="4">
+        <f>R16*1.05</f>
+        <v>0.59849999999999992</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>75</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>68</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>68</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F17" s="6">
         <v>0.86849038461538397</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G17" s="6">
         <f>6.7799419/100</f>
         <v>6.7799419E-2</v>
       </c>
-      <c r="H16" s="7">
-        <f>1-SUM(F16:G16,I16)</f>
+      <c r="H17" s="7">
+        <f>1-SUM(F17:G17,I17)</f>
         <v>1.3710196384616014E-2</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I17" s="5">
         <f>5/100</f>
         <v>0.05</v>
       </c>
-      <c r="J16" s="9">
-        <f t="shared" si="0"/>
+      <c r="J17" s="9">
+        <f>SUM(F17:I17)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K17" s="6">
         <v>0.86599999999999999</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L17" s="6">
         <v>0.75829999999999997</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M17" s="6">
         <v>0.94739999999999991</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N17" s="6">
         <v>0.93709999999999993</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O17" s="6">
         <v>0.87280000000000002</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P17" s="6">
         <v>0.97950000000000004</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q17" s="5">
         <v>0.78</v>
       </c>
-      <c r="R16" s="7">
-        <f>Q16*0.95</f>
+      <c r="R17" s="7">
+        <f>Q17*0.95</f>
         <v>0.74099999999999999</v>
       </c>
-      <c r="S16" s="7">
-        <f>R16*1.05</f>
+      <c r="S17" s="7">
+        <f>R17*1.05</f>
         <v>0.77805000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.73424999999999996</v>
-      </c>
-      <c r="G17" s="6">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="H17" s="7">
-        <f>1-SUM(F17:G17,I17)</f>
-        <v>4.3750000000000067E-2</v>
-      </c>
-      <c r="I17" s="5">
-        <f>13.9/100</f>
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="J17" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0.87980000000000003</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0.82969999999999999</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0.92209999999999992</v>
-      </c>
-      <c r="N17" s="6">
-        <v>0.95669999999999999</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0.8993000000000001</v>
-      </c>
-      <c r="P17" s="6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="Q17" s="5">
-        <f>83.3/100</f>
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="R17" s="5">
-        <f>74.5/100</f>
-        <v>0.745</v>
-      </c>
-      <c r="S17" s="5">
-        <f>92.6/100</f>
-        <v>0.92599999999999993</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
@@ -2516,7 +2520,7 @@
         <v>0.13900000000000001</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F18:I18)</f>
         <v>1</v>
       </c>
       <c r="K18" s="6">
@@ -2538,85 +2542,86 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="Q18" s="5">
+        <f>83.3/100</f>
+        <v>0.83299999999999996</v>
+      </c>
+      <c r="R18" s="5">
+        <f>74.5/100</f>
+        <v>0.745</v>
+      </c>
+      <c r="S18" s="5">
+        <f>92.6/100</f>
+        <v>0.92599999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.73424999999999996</v>
+      </c>
+      <c r="G19" s="6">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="H19" s="7">
+        <f>1-SUM(F19:G19,I19)</f>
+        <v>4.3750000000000067E-2</v>
+      </c>
+      <c r="I19" s="5">
+        <f>13.9/100</f>
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="J19" s="9">
+        <f>SUM(F19:I19)</f>
+        <v>1</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0.87980000000000003</v>
+      </c>
+      <c r="L19" s="6">
+        <v>0.82969999999999999</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0.92209999999999992</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0.95669999999999999</v>
+      </c>
+      <c r="O19" s="6">
+        <v>0.8993000000000001</v>
+      </c>
+      <c r="P19" s="6">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="Q19" s="5">
         <f>81.7/100</f>
         <v>0.81700000000000006</v>
       </c>
-      <c r="R18" s="5">
+      <c r="R19" s="5">
         <f>71.8/100</f>
         <v>0.71799999999999997</v>
       </c>
-      <c r="S18" s="5">
+      <c r="S19" s="5">
         <f>91.6/100</f>
         <v>0.91599999999999993</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5">
-        <f>K19*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="5">
-        <f>L19*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
-        <v>0.95669999999999999</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0.8993000000000001</v>
-      </c>
-      <c r="P19" s="6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="Q19" s="5">
-        <v>0</v>
-      </c>
-      <c r="R19" s="7">
-        <f>Q19*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="7">
-        <f>R19*1.05</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>74</v>
@@ -2643,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F20:I20)</f>
         <v>1</v>
       </c>
       <c r="K20" s="5">
@@ -2680,16 +2685,16 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -2698,49 +2703,53 @@
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5">
         <v>0</v>
       </c>
       <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <f>SUM(F21:I21)</f>
         <v>1</v>
       </c>
-      <c r="J21" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="K21" s="5">
         <v>0</v>
       </c>
       <c r="L21" s="5">
+        <f>K21*0.95</f>
         <v>0</v>
       </c>
       <c r="M21" s="5">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5">
-        <v>0</v>
+        <f>L21*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.95669999999999999</v>
+      </c>
+      <c r="O21" s="6">
+        <v>0.8993000000000001</v>
+      </c>
+      <c r="P21" s="6">
+        <v>0.99199999999999999</v>
       </c>
       <c r="Q21" s="5">
         <v>0</v>
       </c>
-      <c r="R21" s="5">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5">
+      <c r="R21" s="7">
+        <f>Q21*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="7">
+        <f>R21*1.05</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>73</v>
@@ -2749,463 +2758,451 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
       </c>
       <c r="F22" s="5">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>5.2999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H22" s="5">
-        <v>0.46899999999999997</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
-        <v>5.8000000000000003E-2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F22:I22)</f>
         <v>1</v>
       </c>
       <c r="K22" s="5">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="L22" s="10">
-        <f>K22*0.95</f>
-        <v>0.59850000000000003</v>
-      </c>
-      <c r="M22" s="10">
-        <f>L22*1.05</f>
-        <v>0.62842500000000001</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
       </c>
       <c r="N22" s="5">
-        <v>0.95176181599999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="5">
-        <f>N22*0.95</f>
-        <v>0.90417372519999994</v>
+        <v>0</v>
       </c>
       <c r="P22" s="5">
-        <f>N22*1.05</f>
-        <v>0.99934990680000002</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="5">
-        <v>0.71</v>
-      </c>
-      <c r="R22" s="7">
-        <f>Q22*0.95</f>
-        <v>0.67449999999999999</v>
-      </c>
-      <c r="S22" s="7">
-        <f>R22*1.05</f>
-        <v>0.70822499999999999</v>
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
         <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
         <v>69</v>
       </c>
-      <c r="F23">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="G23">
-        <v>4.7E-2</v>
-      </c>
-      <c r="H23">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="I23">
-        <v>5.3999999999999999E-2</v>
+      <c r="F23" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="G23" s="5">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="I23" s="5">
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="0"/>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="K23">
+        <f>SUM(F23:I23)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
         <v>0.63000000000000012</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="10">
         <f>K23*0.95</f>
         <v>0.59850000000000003</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="10">
         <f>L23*1.05</f>
         <v>0.62842500000000001</v>
       </c>
-      <c r="N23">
-        <v>0.93</v>
-      </c>
-      <c r="O23">
+      <c r="N23" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O23" s="5">
         <f>N23*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P23">
-        <f>MIN(N23*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q23">
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="R23" s="4">
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P23" s="5">
+        <f>N23*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="R23" s="7">
         <f>Q23*0.95</f>
-        <v>0.61750000000000005</v>
-      </c>
-      <c r="S23" s="4">
+        <v>0.67449999999999999</v>
+      </c>
+      <c r="S23" s="7">
         <f>R23*1.05</f>
-        <v>0.64837500000000003</v>
+        <v>0.70822499999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="G24">
+        <v>4.7E-2</v>
+      </c>
+      <c r="H24">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I24">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J24" s="9">
+        <f>SUM(F24:I24)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="K24">
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="L24" s="4">
+        <f>K24*0.95</f>
+        <v>0.59850000000000003</v>
+      </c>
+      <c r="M24" s="4">
+        <f>L24*1.05</f>
+        <v>0.62842500000000001</v>
+      </c>
+      <c r="N24">
         <v>0.93</v>
       </c>
-      <c r="G24" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H24" s="7">
-        <f>1-SUM(F24:G24,I24)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K24" s="5">
-        <v>0.622</v>
-      </c>
-      <c r="L24" s="10">
-        <f>K24*0.94</f>
-        <v>0.58467999999999998</v>
-      </c>
-      <c r="M24" s="10">
-        <f>L24*1.06</f>
-        <v>0.6197608</v>
-      </c>
-      <c r="N24" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O24" s="5">
+      <c r="O24">
         <f>N24*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P24" s="5">
-        <f>N24*1.05</f>
-        <v>0.99934990680000002</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="R24" s="7">
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P24">
+        <f>MIN(N24*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q24">
+        <v>0.65000000000000013</v>
+      </c>
+      <c r="R24" s="4">
         <f>Q24*0.95</f>
-        <v>0.57379999999999998</v>
-      </c>
-      <c r="S24" s="7">
+        <v>0.61750000000000005</v>
+      </c>
+      <c r="S24" s="4">
         <f>R24*1.05</f>
-        <v>0.60248999999999997</v>
+        <v>0.64837500000000003</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
         <v>69</v>
       </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0.17899999999999999</v>
+      <c r="F25" s="5">
+        <v>0.93</v>
+      </c>
+      <c r="G25" s="5">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H25" s="7">
         <f>1-SUM(F25:G25,I25)</f>
-        <v>0.1070000000000001</v>
+        <v>0</v>
       </c>
       <c r="I25" s="5">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F25:I25)</f>
         <v>1</v>
       </c>
-      <c r="K25" s="6">
-        <v>0.88470000000000004</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0.84920000000000007</v>
-      </c>
-      <c r="M25" s="6">
-        <v>0.93629999999999991</v>
-      </c>
-      <c r="N25" s="6">
-        <v>0.9466</v>
-      </c>
-      <c r="O25" s="6">
-        <v>0.91510000000000002</v>
-      </c>
-      <c r="P25" s="6">
-        <v>0.97360000000000002</v>
+      <c r="K25" s="5">
+        <v>0.622</v>
+      </c>
+      <c r="L25" s="10">
+        <f>K25*0.94</f>
+        <v>0.58467999999999998</v>
+      </c>
+      <c r="M25" s="10">
+        <f>L25*1.06</f>
+        <v>0.6197608</v>
+      </c>
+      <c r="N25" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O25" s="5">
+        <f>N25*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P25" s="5">
+        <f>N25*1.05</f>
+        <v>0.99934990680000002</v>
       </c>
       <c r="Q25" s="5">
-        <v>0.41000000000000003</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="R25" s="7">
         <f>Q25*0.95</f>
-        <v>0.38950000000000001</v>
+        <v>0.57379999999999998</v>
       </c>
       <c r="S25" s="7">
         <f>R25*1.05</f>
-        <v>0.40897500000000003</v>
+        <v>0.60248999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" s="6">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="H26" s="7">
+        <f>1-SUM(F26:G26,I26)</f>
+        <v>0.1070000000000001</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="J26" s="9">
+        <f>SUM(F26:I26)</f>
+        <v>1</v>
+      </c>
+      <c r="K26" s="6">
+        <v>0.88470000000000004</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0.84920000000000007</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0.93629999999999991</v>
+      </c>
+      <c r="N26" s="6">
+        <v>0.9466</v>
+      </c>
+      <c r="O26" s="6">
+        <v>0.91510000000000002</v>
+      </c>
+      <c r="P26" s="6">
+        <v>0.97360000000000002</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>0.41000000000000003</v>
+      </c>
+      <c r="R26" s="7">
+        <f>Q26*0.95</f>
+        <v>0.38950000000000001</v>
+      </c>
+      <c r="S26" s="7">
+        <f>R26*1.05</f>
+        <v>0.40897500000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="6">
         <v>0.55099999999999993</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G27" s="6">
         <f>26.92252/100</f>
         <v>0.2692252</v>
       </c>
-      <c r="H26" s="7">
-        <f>1-SUM(F26:G26,I26)</f>
+      <c r="H27" s="7">
+        <f>1-SUM(F27:G27,I27)</f>
         <v>4.08748000000001E-2</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I27" s="5">
         <f>13.89/100</f>
         <v>0.1389</v>
       </c>
-      <c r="J26" s="9">
-        <f t="shared" si="0"/>
+      <c r="J27" s="9">
+        <f>SUM(F27:I27)</f>
         <v>1</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K27" s="6">
         <v>0.87769999999999992</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L27" s="6">
         <v>0.86930000000000007</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M27" s="6">
         <v>0.88549999999999995</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N27" s="6">
         <v>0.95109999999999995</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O27" s="6">
         <v>0.93889999999999996</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P27" s="6">
         <v>0.95739999999999992</v>
       </c>
-      <c r="Q26" s="5">
+      <c r="Q27" s="5">
         <v>0.59399999999999997</v>
       </c>
-      <c r="R26" s="5">
-        <f>Q26-3*(2.16/100)</f>
+      <c r="R27" s="5">
+        <f>Q27-3*(2.16/100)</f>
         <v>0.5292</v>
       </c>
-      <c r="S26" s="5">
-        <f>Q26+3*(2.16/100)</f>
+      <c r="S27" s="5">
+        <f>Q27+3*(2.16/100)</f>
         <v>0.65879999999999994</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K27" s="4">
-        <v>0.84588505065844988</v>
-      </c>
-      <c r="L27" s="4">
-        <f>K27*0.95</f>
-        <v>0.80359079812552736</v>
-      </c>
-      <c r="M27" s="4">
-        <f>L27*1.05</f>
-        <v>0.84377033803180379</v>
-      </c>
-      <c r="N27">
-        <v>0.93</v>
-      </c>
-      <c r="O27">
-        <f>N27*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P27">
-        <f>MIN(N27*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>0.71148214285714262</v>
-      </c>
-      <c r="R27" s="4">
-        <f>Q27*0.95</f>
-        <v>0.67590803571428548</v>
-      </c>
-      <c r="S27" s="4">
-        <f>R27*1.05</f>
-        <v>0.70970343749999976</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
         <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="5">
-        <f>AVERAGE(420.2,405.3,420.2,403.8,390.7,468.4)/1000</f>
-        <v>0.41809999999999997</v>
-      </c>
-      <c r="G28" s="5">
-        <f>AVERAGE(175.4,153.9,171.8,132.3,106.7,100.1)/1000</f>
-        <v>0.14003333333333337</v>
-      </c>
-      <c r="H28" s="7">
-        <f>1-SUM(F28:G28,I28)</f>
-        <v>0.41068333333333329</v>
-      </c>
-      <c r="I28" s="5">
-        <f>AVERAGE(28.6,37.6,28,37.3,25.9,29.7)/1000</f>
-        <v>3.1183333333333334E-2</v>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F28:I28)</f>
         <v>1</v>
       </c>
-      <c r="K28" s="5">
-        <f>AVERAGE(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.89050000000000007</v>
-      </c>
-      <c r="L28" s="5">
-        <f>MIN(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.879</v>
-      </c>
-      <c r="M28" s="5">
-        <f>MAX(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
-        <v>0.90099999999999991</v>
-      </c>
-      <c r="N28" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O28" s="5">
+      <c r="K28" s="4">
+        <v>0.84588505065844988</v>
+      </c>
+      <c r="L28" s="4">
+        <f>K28*0.95</f>
+        <v>0.80359079812552736</v>
+      </c>
+      <c r="M28" s="4">
+        <f>L28*1.05</f>
+        <v>0.84377033803180379</v>
+      </c>
+      <c r="N28">
+        <v>0.93</v>
+      </c>
+      <c r="O28">
         <f>N28*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P28" s="5">
-        <f>N28*1.05</f>
-        <v>0.99934990680000002</v>
-      </c>
-      <c r="Q28" s="5">
-        <f>AVERAGE(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.79749999999999999</v>
-      </c>
-      <c r="R28" s="5">
-        <f>MIN(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="S28" s="5">
-        <f>MAX(79.7,80.2,80,80,81.2,77.4)/100</f>
-        <v>0.81200000000000006</v>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P28">
+        <f>MIN(N28*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0.71148214285714262</v>
+      </c>
+      <c r="R28" s="4">
+        <f>Q28*0.95</f>
+        <v>0.67590803571428548</v>
+      </c>
+      <c r="S28" s="4">
+        <f>R28*1.05</f>
+        <v>0.70970343749999976</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
         <v>73</v>
@@ -3236,7 +3233,7 @@
         <v>3.1183333333333334E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F29:I29)</f>
         <v>1</v>
       </c>
       <c r="K29" s="5">
@@ -3277,10 +3274,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>68</v>
@@ -3289,106 +3286,115 @@
         <v>68</v>
       </c>
       <c r="E30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="5">
+        <f>AVERAGE(420.2,405.3,420.2,403.8,390.7,468.4)/1000</f>
+        <v>0.41809999999999997</v>
+      </c>
+      <c r="G30" s="5">
+        <f>AVERAGE(175.4,153.9,171.8,132.3,106.7,100.1)/1000</f>
+        <v>0.14003333333333337</v>
+      </c>
+      <c r="H30" s="7">
+        <f>1-SUM(F30:G30,I30)</f>
+        <v>0.41068333333333329</v>
+      </c>
+      <c r="I30" s="5">
+        <f>AVERAGE(28.6,37.6,28,37.3,25.9,29.7)/1000</f>
+        <v>3.1183333333333334E-2</v>
+      </c>
+      <c r="J30" s="9">
+        <f>SUM(F30:I30)</f>
+        <v>1</v>
+      </c>
+      <c r="K30" s="5">
+        <f>AVERAGE(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.89050000000000007</v>
+      </c>
+      <c r="L30" s="5">
+        <f>MIN(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.879</v>
+      </c>
+      <c r="M30" s="5">
+        <f>MAX(89.5,89.3,87.9,88.2,89.3,90.1)/100</f>
+        <v>0.90099999999999991</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O30" s="5">
+        <f>N30*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P30" s="5">
+        <f>N30*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q30" s="5">
+        <f>AVERAGE(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.79749999999999999</v>
+      </c>
+      <c r="R30" s="5">
+        <f>MIN(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="S30" s="5">
+        <f>MAX(79.7,80.2,80,80,81.2,77.4)/100</f>
+        <v>0.81200000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="6">
+      <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="6">
         <v>0.53783333333333327</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G31" s="6">
         <f>13.249433/100</f>
         <v>0.13249432999999999</v>
       </c>
-      <c r="H30" s="7">
-        <f>1-SUM(F30:G30,I30)</f>
-        <v>2.4672336666666794E-2</v>
-      </c>
-      <c r="I30" s="5">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K30" s="6">
-        <v>0.83030000000000004</v>
-      </c>
-      <c r="L30" s="6">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="M30" s="6">
-        <v>0.9194</v>
-      </c>
-      <c r="N30" s="6">
-        <v>0.93189999999999995</v>
-      </c>
-      <c r="O30" s="6">
-        <v>0.86629999999999996</v>
-      </c>
-      <c r="P30" s="6">
-        <v>0.96779999999999999</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>0.68700000000000006</v>
-      </c>
-      <c r="R30" s="10">
-        <f>Q30*0.95</f>
-        <v>0.65265000000000006</v>
-      </c>
-      <c r="S30" s="10">
-        <f>R30*1.05</f>
-        <v>0.68528250000000013</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0.56188888888888899</v>
-      </c>
-      <c r="G31" s="6">
-        <v>8.6999999999999994E-2</v>
-      </c>
       <c r="H31" s="7">
         <f>1-SUM(F31:G31,I31)</f>
-        <v>0.23711111111111105</v>
-      </c>
-      <c r="I31" s="8">
-        <v>0.114</v>
+        <v>2.4672336666666794E-2</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0.30499999999999999</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F31:I31)</f>
         <v>1</v>
       </c>
       <c r="K31" s="6">
-        <v>0.81159999999999999</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="L31" s="6">
-        <v>0.70010000000000006</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="M31" s="6">
-        <v>0.93319999999999992</v>
+        <v>0.9194</v>
       </c>
       <c r="N31" s="6">
-        <v>0.95489999999999997</v>
+        <v>0.93189999999999995</v>
       </c>
       <c r="O31" s="6">
-        <v>0.90229999999999999</v>
+        <v>0.86629999999999996</v>
       </c>
       <c r="P31" s="6">
-        <v>0.98790000000000011</v>
+        <v>0.96779999999999999</v>
       </c>
       <c r="Q31" s="5">
         <v>0.68700000000000006</v>
@@ -3404,441 +3410,438 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
+        <v>68</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.56188888888888899</v>
+      </c>
+      <c r="G32" s="6">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="H32" s="7">
+        <f>1-SUM(F32:G32,I32)</f>
+        <v>0.23711111111111105</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0.114</v>
+      </c>
+      <c r="J32" s="9">
+        <f>SUM(F32:I32)</f>
         <v>1</v>
       </c>
-      <c r="J32" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K32" s="5">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5">
-        <f>N32*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="5">
-        <f>N32*1.05</f>
-        <v>0</v>
+      <c r="K32" s="6">
+        <v>0.81159999999999999</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.70010000000000006</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.93319999999999992</v>
+      </c>
+      <c r="N32" s="6">
+        <v>0.95489999999999997</v>
+      </c>
+      <c r="O32" s="6">
+        <v>0.90229999999999999</v>
+      </c>
+      <c r="P32" s="6">
+        <v>0.98790000000000011</v>
       </c>
       <c r="Q32" s="5">
-        <v>0</v>
+        <v>0.68700000000000006</v>
       </c>
       <c r="R32" s="10">
         <f>Q32*0.95</f>
-        <v>0</v>
+        <v>0.65265000000000006</v>
       </c>
       <c r="S32" s="10">
         <f>R32*1.05</f>
-        <v>0</v>
+        <v>0.68528250000000013</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
         <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0.62166666666666659</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0.122</v>
-      </c>
-      <c r="H33" s="7">
-        <f>1-SUM(F33:G33,I33)</f>
-        <v>0.14233333333333342</v>
-      </c>
-      <c r="I33" s="8">
-        <v>0.114</v>
+        <v>69</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5">
+        <v>1</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F33:I33)</f>
         <v>1</v>
       </c>
-      <c r="K33" s="6">
-        <v>0.78639999999999999</v>
-      </c>
-      <c r="L33" s="6">
-        <v>0.71209999999999996</v>
-      </c>
-      <c r="M33" s="6">
-        <v>0.84200000000000008</v>
-      </c>
-      <c r="N33" s="6">
-        <v>0.9325</v>
-      </c>
-      <c r="O33" s="6">
-        <v>0.91139999999999999</v>
-      </c>
-      <c r="P33" s="6">
-        <v>0.94950000000000001</v>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <f>N33*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="5">
+        <f>N33*1.05</f>
+        <v>0</v>
       </c>
       <c r="Q33" s="5">
-        <v>0.68900000000000006</v>
+        <v>0</v>
       </c>
       <c r="R33" s="10">
         <f>Q33*0.95</f>
-        <v>0.65455000000000008</v>
+        <v>0</v>
       </c>
       <c r="S33" s="10">
         <f>R33*1.05</f>
-        <v>0.6872775000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0</v>
-      </c>
-      <c r="G34" s="8">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.62166666666666659</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.122</v>
+      </c>
+      <c r="H34" s="7">
+        <f>1-SUM(F34:G34,I34)</f>
+        <v>0.14233333333333342</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0.114</v>
+      </c>
+      <c r="J34" s="9">
+        <f>SUM(F34:I34)</f>
         <v>1</v>
       </c>
-      <c r="H34" s="8">
-        <v>0</v>
-      </c>
-      <c r="I34" s="8">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K34" s="8">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8">
-        <v>0</v>
-      </c>
-      <c r="N34" s="8">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="O34" s="8">
-        <v>0</v>
-      </c>
-      <c r="P34" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>0</v>
-      </c>
-      <c r="R34" s="8">
-        <v>0</v>
-      </c>
-      <c r="S34" s="8">
-        <v>0</v>
+      <c r="K34" s="6">
+        <v>0.78639999999999999</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.71209999999999996</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.84200000000000008</v>
+      </c>
+      <c r="N34" s="6">
+        <v>0.9325</v>
+      </c>
+      <c r="O34" s="6">
+        <v>0.91139999999999999</v>
+      </c>
+      <c r="P34" s="6">
+        <v>0.94950000000000001</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>0.68900000000000006</v>
+      </c>
+      <c r="R34" s="10">
+        <f>Q34*0.95</f>
+        <v>0.65455000000000008</v>
+      </c>
+      <c r="S34" s="10">
+        <f>R34*1.05</f>
+        <v>0.6872775000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
         <v>73</v>
       </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35">
-        <v>0.23</v>
-      </c>
-      <c r="G35">
-        <v>0.01</v>
-      </c>
-      <c r="H35">
-        <v>0.45</v>
-      </c>
-      <c r="I35">
-        <v>0.31</v>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>1</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F35:I35)</f>
         <v>1</v>
       </c>
-      <c r="K35">
-        <v>0.8</v>
-      </c>
-      <c r="L35" s="4">
-        <f>K35*0.95</f>
-        <v>0.76</v>
-      </c>
-      <c r="M35" s="4">
-        <f>L35*1.05</f>
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="N35">
-        <v>0.93</v>
-      </c>
-      <c r="O35">
-        <f t="shared" ref="O35:O40" si="1">N35*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P35">
-        <f>MIN(N35*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q35">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R35" s="4">
-        <f t="shared" ref="R35:R43" si="2">Q35*0.95</f>
-        <v>0.55099999999999993</v>
-      </c>
-      <c r="S35" s="4">
-        <f t="shared" ref="S35:S43" si="3">R35*1.05</f>
-        <v>0.57855000000000001</v>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="O35" s="8">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>0</v>
+      </c>
+      <c r="R35" s="8">
+        <v>0</v>
+      </c>
+      <c r="S35" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>73</v>
       </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
       <c r="E36" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="5">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="G36" s="5">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="H36" s="9">
-        <f>1-F36-G36-I36</f>
-        <v>0.37699999999999995</v>
-      </c>
-      <c r="I36" s="5">
-        <v>6.9000000000000006E-2</v>
+      <c r="F36">
+        <v>0.23</v>
+      </c>
+      <c r="G36">
+        <v>0.01</v>
+      </c>
+      <c r="H36">
+        <v>0.45</v>
+      </c>
+      <c r="I36">
+        <v>0.31</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F36:I36)</f>
         <v>1</v>
       </c>
-      <c r="K36" s="15">
-        <v>0.81</v>
+      <c r="K36">
+        <v>0.8</v>
       </c>
       <c r="L36" s="4">
         <f>K36*0.95</f>
-        <v>0.76949999999999996</v>
+        <v>0.76</v>
       </c>
       <c r="M36" s="4">
         <f>L36*1.05</f>
-        <v>0.807975</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="N36">
-        <v>0.96</v>
-      </c>
-      <c r="O36" s="4">
-        <f t="shared" si="1"/>
-        <v>0.91199999999999992</v>
-      </c>
-      <c r="P36" s="4">
-        <f>O36*1.05</f>
-        <v>0.95760000000000001</v>
+        <v>0.93</v>
+      </c>
+      <c r="O36">
+        <f>N36*0.95</f>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P36">
+        <f>MIN(N36*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
       </c>
       <c r="Q36">
-        <v>0.71</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="R36" s="4">
-        <f t="shared" si="2"/>
-        <v>0.67449999999999999</v>
+        <f>Q36*0.95</f>
+        <v>0.55099999999999993</v>
       </c>
       <c r="S36" s="4">
-        <f t="shared" si="3"/>
-        <v>0.70822499999999999</v>
+        <f>R36*1.05</f>
+        <v>0.57855000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" t="s">
-        <v>68</v>
-      </c>
       <c r="E37" t="s">
         <v>69</v>
       </c>
       <c r="F37" s="5">
-        <v>0.84</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="G37" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="H37" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="H37" s="9">
+        <f>1-F37-G37-I37</f>
+        <v>0.37699999999999995</v>
       </c>
       <c r="I37" s="5">
-        <v>0.04</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F37:I37)</f>
         <v>1</v>
       </c>
-      <c r="K37" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="L37" s="10">
-        <f>K37*0.94</f>
-        <v>0.82719999999999994</v>
-      </c>
-      <c r="M37" s="10">
-        <f>L37*1.06</f>
-        <v>0.87683199999999994</v>
-      </c>
-      <c r="N37" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O37" s="5">
-        <f t="shared" si="1"/>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P37" s="5">
-        <f>N37*1.05</f>
-        <v>0.99934990680000002</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>0.77</v>
-      </c>
-      <c r="R37" s="10">
-        <f t="shared" si="2"/>
-        <v>0.73149999999999993</v>
-      </c>
-      <c r="S37" s="10">
-        <f t="shared" si="3"/>
-        <v>0.76807499999999995</v>
+      <c r="K37" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="L37" s="4">
+        <f>K37*0.95</f>
+        <v>0.76949999999999996</v>
+      </c>
+      <c r="M37" s="4">
+        <f>L37*1.05</f>
+        <v>0.807975</v>
+      </c>
+      <c r="N37">
+        <v>0.96</v>
+      </c>
+      <c r="O37" s="4">
+        <f>N37*0.95</f>
+        <v>0.91199999999999992</v>
+      </c>
+      <c r="P37" s="4">
+        <f>O37*1.05</f>
+        <v>0.95760000000000001</v>
+      </c>
+      <c r="Q37">
+        <v>0.71</v>
+      </c>
+      <c r="R37" s="4">
+        <f>Q37*0.95</f>
+        <v>0.67449999999999999</v>
+      </c>
+      <c r="S37" s="4">
+        <f>R37*1.05</f>
+        <v>0.70822499999999999</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
         <v>69</v>
       </c>
-      <c r="F38">
-        <v>0.23</v>
-      </c>
-      <c r="G38">
-        <v>0.01</v>
-      </c>
-      <c r="H38">
-        <v>0.45</v>
-      </c>
-      <c r="I38">
-        <v>0.31</v>
+      <c r="F38" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="G38" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="H38" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.04</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F38:I38)</f>
         <v>1</v>
       </c>
-      <c r="K38">
-        <v>0.8</v>
-      </c>
-      <c r="L38" s="4">
-        <f>K38*0.95</f>
-        <v>0.76</v>
-      </c>
-      <c r="M38" s="4">
-        <f>L38*1.05</f>
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="N38">
-        <v>0.93</v>
-      </c>
-      <c r="O38">
-        <f t="shared" si="1"/>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P38">
-        <f>MIN(N38*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q38">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R38" s="4">
-        <f t="shared" si="2"/>
-        <v>0.55099999999999993</v>
-      </c>
-      <c r="S38" s="4">
-        <f t="shared" si="3"/>
-        <v>0.57855000000000001</v>
+      <c r="K38" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="L38" s="10">
+        <f>K38*0.94</f>
+        <v>0.82719999999999994</v>
+      </c>
+      <c r="M38" s="10">
+        <f>L38*1.06</f>
+        <v>0.87683199999999994</v>
+      </c>
+      <c r="N38" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O38" s="5">
+        <f>N38*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P38" s="5">
+        <f>N38*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="R38" s="10">
+        <f>Q38*0.95</f>
+        <v>0.73149999999999993</v>
+      </c>
+      <c r="S38" s="10">
+        <f>R38*1.05</f>
+        <v>0.76807499999999995</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
@@ -3865,7 +3868,7 @@
         <v>0.31</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F39:I39)</f>
         <v>1</v>
       </c>
       <c r="K39">
@@ -3883,7 +3886,7 @@
         <v>0.93</v>
       </c>
       <c r="O39">
-        <f t="shared" si="1"/>
+        <f>N39*0.95</f>
         <v>0.88349999999999995</v>
       </c>
       <c r="P39">
@@ -3894,84 +3897,83 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" si="2"/>
+        <f>Q39*0.95</f>
         <v>0.55099999999999993</v>
       </c>
       <c r="S39" s="4">
-        <f t="shared" si="3"/>
+        <f>R39*1.05</f>
         <v>0.57855000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
         <v>69</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40">
+        <v>0.23</v>
+      </c>
+      <c r="G40">
+        <v>0.01</v>
+      </c>
+      <c r="H40">
+        <v>0.45</v>
+      </c>
+      <c r="I40">
+        <v>0.31</v>
+      </c>
+      <c r="J40" s="9">
+        <f>SUM(F40:I40)</f>
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>0.8</v>
+      </c>
+      <c r="L40" s="4">
+        <f>K40*0.95</f>
+        <v>0.76</v>
+      </c>
+      <c r="M40" s="4">
+        <f>L40*1.05</f>
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="N40">
         <v>0.93</v>
       </c>
-      <c r="G40" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H40" s="7">
-        <f>1-SUM(F40:G40,I40)</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="5">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K40" s="5">
-        <v>0.622</v>
-      </c>
-      <c r="L40" s="10">
-        <f>K40*0.94</f>
-        <v>0.58467999999999998</v>
-      </c>
-      <c r="M40" s="10">
-        <f>L40*1.06</f>
-        <v>0.6197608</v>
-      </c>
-      <c r="N40" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O40" s="5">
-        <f t="shared" si="1"/>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P40" s="5">
-        <f>N40*1.05</f>
-        <v>0.99934990680000002</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="R40" s="7">
-        <f t="shared" si="2"/>
-        <v>0.57379999999999998</v>
-      </c>
-      <c r="S40" s="7">
-        <f t="shared" si="3"/>
-        <v>0.60248999999999997</v>
+      <c r="O40">
+        <f>N40*0.95</f>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P40">
+        <f>MIN(N40*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q40">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R40" s="4">
+        <f>Q40*0.95</f>
+        <v>0.55099999999999993</v>
+      </c>
+      <c r="S40" s="4">
+        <f>R40*1.05</f>
+        <v>0.57855000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
         <v>75</v>
@@ -3983,98 +3985,101 @@
         <v>68</v>
       </c>
       <c r="E41" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="5">
+        <v>0.93</v>
+      </c>
+      <c r="G41" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H41" s="7">
+        <f>1-SUM(F41:G41,I41)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="5">
+        <v>0</v>
+      </c>
+      <c r="J41" s="9">
+        <f>SUM(F41:I41)</f>
+        <v>1</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.622</v>
+      </c>
+      <c r="L41" s="10">
+        <f>K41*0.94</f>
+        <v>0.58467999999999998</v>
+      </c>
+      <c r="M41" s="10">
+        <f>L41*1.06</f>
+        <v>0.6197608</v>
+      </c>
+      <c r="N41" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O41" s="5">
+        <f>N41*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P41" s="5">
+        <f>N41*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="R41" s="7">
+        <f>Q41*0.95</f>
+        <v>0.57379999999999998</v>
+      </c>
+      <c r="S41" s="7">
+        <f>R41*1.05</f>
+        <v>0.60248999999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" t="s">
         <v>68</v>
       </c>
-      <c r="F41" s="6">
+      <c r="D42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42" s="6">
         <v>0.72292857142857125</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G42" s="6">
         <f>11.68969/100</f>
         <v>0.11689690000000001</v>
       </c>
-      <c r="H41" s="7">
-        <f>1-SUM(F41:G41,I41)</f>
+      <c r="H42" s="7">
+        <f>1-SUM(F42:G42,I42)</f>
         <v>5.4174528571428793E-2</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I42" s="5">
         <v>0.106</v>
       </c>
-      <c r="J41" s="9">
-        <f t="shared" si="0"/>
+      <c r="J42" s="9">
+        <f>SUM(F42:I42)</f>
         <v>1</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K42" s="6">
         <v>0.86609999999999998</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L42" s="6">
         <v>0.79749999999999999</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M42" s="6">
         <v>0.93370000000000009</v>
-      </c>
-      <c r="N41" s="6">
-        <v>0.94900000000000007</v>
-      </c>
-      <c r="O41" s="6">
-        <v>0.90069999999999995</v>
-      </c>
-      <c r="P41" s="6">
-        <v>0.98250000000000004</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="R41" s="10">
-        <f t="shared" si="2"/>
-        <v>0.65454999999999997</v>
-      </c>
-      <c r="S41" s="10">
-        <f t="shared" si="3"/>
-        <v>0.68727749999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" s="5">
-        <v>0</v>
-      </c>
-      <c r="G42" s="5">
-        <v>1</v>
-      </c>
-      <c r="H42" s="5">
-        <v>0</v>
-      </c>
-      <c r="I42" s="5">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K42" s="5">
-        <v>0</v>
-      </c>
-      <c r="L42" s="5">
-        <f>K42*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="5">
-        <f>L42*1.05</f>
-        <v>0</v>
       </c>
       <c r="N42" s="6">
         <v>0.94900000000000007</v>
@@ -4086,20 +4091,20 @@
         <v>0.98250000000000004</v>
       </c>
       <c r="Q42" s="5">
-        <v>0</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>Q42*0.95</f>
+        <v>0.65454999999999997</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>R42*1.05</f>
+        <v>0.68727749999999999</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
         <v>75</v>
@@ -4111,156 +4116,161 @@
         <v>68</v>
       </c>
       <c r="E43" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43" s="5">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9">
+        <f>SUM(F43:I43)</f>
+        <v>1</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5">
+        <f>K43*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="5">
+        <f>L43*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="6">
+        <v>0.94900000000000007</v>
+      </c>
+      <c r="O43" s="6">
+        <v>0.90069999999999995</v>
+      </c>
+      <c r="P43" s="6">
+        <v>0.98250000000000004</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
+      <c r="R43" s="10">
+        <f>Q43*0.95</f>
+        <v>0</v>
+      </c>
+      <c r="S43" s="10">
+        <f>R43*1.05</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" t="s">
         <v>68</v>
       </c>
-      <c r="F43" s="6">
+      <c r="D44" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="6">
         <f>81.85/100</f>
         <v>0.81849999999999989</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G44" s="6">
         <f>0.1448625</f>
         <v>0.14486250000000001</v>
       </c>
-      <c r="H43" s="7">
-        <f>1-SUM(F43:G43,I43)</f>
+      <c r="H44" s="7">
+        <f>1-SUM(F44:G44,I44)</f>
         <v>6.6375000000000739E-3</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I44" s="5">
         <v>0.03</v>
       </c>
-      <c r="J43" s="9">
-        <f t="shared" si="0"/>
+      <c r="J44" s="9">
+        <f>SUM(F44:I44)</f>
         <v>1</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K44" s="6">
         <v>0.88379999999999992</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L44" s="6">
         <v>0.87650000000000006</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M44" s="6">
         <v>0.88790000000000002</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N44" s="6">
         <v>0.96579999999999999</v>
       </c>
-      <c r="O43" s="6">
+      <c r="O44" s="6">
         <v>0.94930000000000003</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P44" s="6">
         <v>0.98499999999999999</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q44" s="5">
         <v>0.88000000000000012</v>
       </c>
-      <c r="R43" s="10">
-        <f t="shared" si="2"/>
+      <c r="R44" s="10">
+        <f>Q44*0.95</f>
         <v>0.83600000000000008</v>
       </c>
-      <c r="S43" s="10">
-        <f t="shared" si="3"/>
+      <c r="S44" s="10">
+        <f>R44*1.05</f>
         <v>0.87780000000000014</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" t="s">
-        <v>73</v>
-      </c>
-      <c r="E44" t="s">
-        <v>69</v>
-      </c>
-      <c r="F44">
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="G44" s="5">
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="H44" s="9">
-        <f>1-F44-G44-I44</f>
-        <v>0.65700000000000003</v>
-      </c>
-      <c r="I44" s="5">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="J44" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K44" s="9">
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="N44">
-        <v>0.96</v>
-      </c>
-      <c r="Q44" s="17">
-        <v>0.83699999999999997</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E45" t="s">
         <v>69</v>
       </c>
-      <c r="F45" s="15">
-        <v>0.47899999999999998</v>
-      </c>
-      <c r="G45" s="15">
-        <v>3.9E-2</v>
+      <c r="F45">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="G45" s="5">
+        <v>0.13200000000000001</v>
       </c>
       <c r="H45" s="9">
-        <f>1-I45-F45-G45</f>
-        <v>7.5999999999999984E-2</v>
-      </c>
-      <c r="I45" s="15">
-        <v>0.40600000000000003</v>
+        <f>1-F45-G45-I45</f>
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="I45" s="5">
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="J45" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F45:I45)</f>
         <v>1</v>
       </c>
-      <c r="K45" s="10">
-        <v>0.83</v>
-      </c>
-      <c r="L45" s="10">
-        <f>K45*0.95</f>
-        <v>0.78849999999999998</v>
-      </c>
-      <c r="M45" s="10">
-        <f>K45*1.05</f>
-        <v>0.87149999999999994</v>
-      </c>
-      <c r="N45" s="10">
-        <v>0.95669999999999999</v>
-      </c>
-      <c r="O45" s="10">
-        <v>0.8993000000000001</v>
-      </c>
-      <c r="P45" s="10">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="Q45" s="8">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="R45" s="10">
-        <f>71.8/100</f>
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="S45" s="10">
-        <f>91.6/100</f>
-        <v>0.91599999999999993</v>
+      <c r="K45" s="9">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="N45">
+        <v>0.96</v>
+      </c>
+      <c r="Q45" s="17">
+        <v>0.83699999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
         <v>74</v>
@@ -4268,21 +4278,21 @@
       <c r="E46" t="s">
         <v>69</v>
       </c>
-      <c r="F46" s="9">
-        <v>0.63500000000000001</v>
+      <c r="F46" s="15">
+        <v>0.47899999999999998</v>
       </c>
       <c r="G46" s="15">
-        <v>0.05</v>
+        <v>3.9E-2</v>
       </c>
       <c r="H46" s="9">
         <f>1-I46-F46-G46</f>
-        <v>0.13799999999999996</v>
+        <v>7.5999999999999984E-2</v>
       </c>
       <c r="I46" s="15">
-        <v>0.17699999999999999</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="J46" s="9">
-        <f t="shared" ref="J46" si="4">SUM(F46:I46)</f>
+        <f>SUM(F46:I46)</f>
         <v>1</v>
       </c>
       <c r="K46" s="10">
@@ -4306,7 +4316,7 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="Q46" s="8">
-        <v>0.88200000000000001</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="R46" s="10">
         <f>71.8/100</f>
@@ -4319,73 +4329,69 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s">
         <v>69</v>
       </c>
-      <c r="D47" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" t="s">
-        <v>68</v>
-      </c>
-      <c r="F47" s="6">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="G47" s="6">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="H47" s="7">
-        <f>1-SUM(F47:G47,I47)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="8">
-        <v>0.14000000000000001</v>
+      <c r="F47" s="9">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="H47" s="9">
+        <f>1-I47-F47-G47</f>
+        <v>0.13799999999999996</v>
+      </c>
+      <c r="I47" s="15">
+        <v>0.17699999999999999</v>
       </c>
       <c r="J47" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F47:I47)</f>
         <v>1</v>
       </c>
-      <c r="K47" s="6">
-        <v>0.94140000000000001</v>
-      </c>
-      <c r="L47" s="6">
-        <v>0.92920000000000003</v>
-      </c>
-      <c r="M47" s="6">
-        <v>0.95040000000000002</v>
-      </c>
-      <c r="N47" s="6">
-        <v>0.97010000000000007</v>
-      </c>
-      <c r="O47" s="6">
-        <v>0.96840000000000004</v>
-      </c>
-      <c r="P47" s="6">
-        <v>0.97239999999999993</v>
-      </c>
-      <c r="Q47" s="5">
-        <v>0.68000000000000016</v>
+      <c r="K47" s="10">
+        <v>0.83</v>
+      </c>
+      <c r="L47" s="10">
+        <f>K47*0.95</f>
+        <v>0.78849999999999998</v>
+      </c>
+      <c r="M47" s="10">
+        <f>K47*1.05</f>
+        <v>0.87149999999999994</v>
+      </c>
+      <c r="N47" s="10">
+        <v>0.95669999999999999</v>
+      </c>
+      <c r="O47" s="10">
+        <v>0.8993000000000001</v>
+      </c>
+      <c r="P47" s="10">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="Q47" s="8">
+        <v>0.88200000000000001</v>
       </c>
       <c r="R47" s="10">
-        <f>Q47*0.95</f>
-        <v>0.64600000000000013</v>
+        <f>71.8/100</f>
+        <v>0.71799999999999997</v>
       </c>
       <c r="S47" s="10">
-        <f>R47*1.05</f>
-        <v>0.67830000000000013</v>
+        <f>91.6/100</f>
+        <v>0.91599999999999993</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" t="s">
         <v>69</v>
@@ -4397,118 +4403,118 @@
         <v>68</v>
       </c>
       <c r="F48" s="6">
-        <v>0.65300000000000002</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="G48" s="6">
-        <v>0.02</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="H48" s="7">
         <f>1-SUM(F48:G48,I48)</f>
-        <v>0.2569999999999999</v>
-      </c>
-      <c r="I48" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0.14000000000000001</v>
       </c>
       <c r="J48" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F48:I48)</f>
         <v>1</v>
       </c>
       <c r="K48" s="6">
-        <v>0.89379999999999993</v>
+        <v>0.94140000000000001</v>
       </c>
       <c r="L48" s="6">
-        <v>0.8881</v>
+        <v>0.92920000000000003</v>
       </c>
       <c r="M48" s="6">
-        <v>0.89969999999999994</v>
+        <v>0.95040000000000002</v>
       </c>
       <c r="N48" s="6">
-        <v>0.95799999999999996</v>
+        <v>0.97010000000000007</v>
       </c>
       <c r="O48" s="6">
-        <v>0.9323999999999999</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="P48" s="6">
-        <v>0.97730000000000006</v>
+        <v>0.97239999999999993</v>
       </c>
       <c r="Q48" s="5">
-        <v>0.82</v>
+        <v>0.68000000000000016</v>
       </c>
       <c r="R48" s="10">
         <f>Q48*0.95</f>
-        <v>0.77899999999999991</v>
+        <v>0.64600000000000013</v>
       </c>
       <c r="S48" s="10">
         <f>R48*1.05</f>
-        <v>0.81794999999999995</v>
+        <v>0.67830000000000013</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
         <v>73</v>
       </c>
       <c r="C49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" t="s">
         <v>68</v>
       </c>
-      <c r="D49" t="s">
-        <v>69</v>
-      </c>
       <c r="E49" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" s="5">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5">
+        <v>68</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="H49" s="7">
+        <f>1-SUM(F49:G49,I49)</f>
+        <v>0.2569999999999999</v>
+      </c>
+      <c r="I49" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J49" s="9">
+        <f>SUM(F49:I49)</f>
         <v>1</v>
       </c>
-      <c r="H49" s="5">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0</v>
-      </c>
-      <c r="J49" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K49" s="5">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5">
-        <v>0</v>
-      </c>
-      <c r="M49" s="5">
-        <v>0</v>
-      </c>
-      <c r="N49" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O49" s="5">
-        <f>N49*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P49" s="5">
-        <f>N49*1.05</f>
-        <v>0.99934990680000002</v>
+      <c r="K49" s="6">
+        <v>0.89379999999999993</v>
+      </c>
+      <c r="L49" s="6">
+        <v>0.8881</v>
+      </c>
+      <c r="M49" s="6">
+        <v>0.89969999999999994</v>
+      </c>
+      <c r="N49" s="6">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="O49" s="6">
+        <v>0.9323999999999999</v>
+      </c>
+      <c r="P49" s="6">
+        <v>0.97730000000000006</v>
       </c>
       <c r="Q49" s="5">
-        <v>0</v>
-      </c>
-      <c r="R49" s="7">
-        <v>0</v>
-      </c>
-      <c r="S49" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="R49" s="10">
+        <f>Q49*0.95</f>
+        <v>0.77899999999999991</v>
+      </c>
+      <c r="S49" s="10">
         <f>R49*1.05</f>
-        <v>0</v>
+        <v>0.81794999999999995</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
         <v>73</v>
@@ -4517,37 +4523,35 @@
         <v>68</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
-      </c>
-      <c r="F50" s="6">
-        <v>0.66174999999999995</v>
-      </c>
-      <c r="G50" s="6">
-        <f>1.126924/100</f>
-        <v>1.126924E-2</v>
-      </c>
-      <c r="H50" s="7">
-        <f>1-SUM(F50:G50,I50)</f>
-        <v>0.25398076000000014</v>
+        <v>69</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
       </c>
       <c r="I50" s="5">
-        <v>7.2999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F50:I50)</f>
         <v>1</v>
       </c>
-      <c r="K50" s="6">
-        <v>0.87599999999999989</v>
-      </c>
-      <c r="L50" s="6">
-        <v>0.8206</v>
-      </c>
-      <c r="M50" s="6">
-        <v>0.92709999999999992</v>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5">
+        <v>0</v>
       </c>
       <c r="N50" s="5">
         <v>0.95176181599999998</v>
@@ -4561,140 +4565,147 @@
         <v>0.99934990680000002</v>
       </c>
       <c r="Q50" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="R50" s="10">
-        <f>Q50*0.95</f>
-        <v>0.83124999999999993</v>
-      </c>
-      <c r="S50" s="10">
+        <v>0</v>
+      </c>
+      <c r="R50" s="7">
+        <v>0</v>
+      </c>
+      <c r="S50" s="7">
         <f>R50*1.05</f>
-        <v>0.87281249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="G51">
-        <v>6.0999999999999999E-2</v>
+        <v>68</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0.66174999999999995</v>
+      </c>
+      <c r="G51" s="6">
+        <f>1.126924/100</f>
+        <v>1.126924E-2</v>
       </c>
       <c r="H51" s="7">
         <f>1-SUM(F51:G51,I51)</f>
-        <v>0.21199999999999997</v>
-      </c>
-      <c r="I51">
-        <v>8.8999999999999996E-2</v>
+        <v>0.25398076000000014</v>
+      </c>
+      <c r="I51" s="5">
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="J51" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F51:I51)</f>
         <v>1</v>
       </c>
-      <c r="K51">
-        <v>0.81</v>
-      </c>
-      <c r="L51" s="4">
-        <f>K51*0.95</f>
-        <v>0.76949999999999996</v>
-      </c>
-      <c r="M51" s="4">
-        <f>L51*1.05</f>
-        <v>0.807975</v>
-      </c>
-      <c r="N51">
-        <v>0.93</v>
-      </c>
-      <c r="O51">
+      <c r="K51" s="6">
+        <v>0.87599999999999989</v>
+      </c>
+      <c r="L51" s="6">
+        <v>0.8206</v>
+      </c>
+      <c r="M51" s="6">
+        <v>0.92709999999999992</v>
+      </c>
+      <c r="N51" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O51" s="5">
         <f>N51*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P51">
-        <f>MIN(N51*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q51">
-        <v>0.72</v>
-      </c>
-      <c r="R51" s="4">
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P51" s="5">
+        <f>N51*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="R51" s="10">
         <f>Q51*0.95</f>
-        <v>0.68399999999999994</v>
-      </c>
-      <c r="S51" s="4">
+        <v>0.83124999999999993</v>
+      </c>
+      <c r="S51" s="10">
         <f>R51*1.05</f>
-        <v>0.71819999999999995</v>
+        <v>0.87281249999999999</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
       </c>
       <c r="E52" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="5">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5">
+      <c r="F52">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="G52">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="H52" s="7">
+        <f>1-SUM(F52:G52,I52)</f>
+        <v>0.21199999999999997</v>
+      </c>
+      <c r="I52">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="J52" s="9">
+        <f>SUM(F52:I52)</f>
         <v>1</v>
       </c>
-      <c r="H52" s="5">
-        <v>0</v>
-      </c>
-      <c r="I52" s="5">
-        <v>0</v>
-      </c>
-      <c r="J52" s="9">
-        <f t="shared" ref="J52" si="5">SUM(F52:I52)</f>
-        <v>1</v>
-      </c>
-      <c r="K52" s="5">
-        <v>0</v>
-      </c>
-      <c r="L52" s="5">
+      <c r="K52">
+        <v>0.81</v>
+      </c>
+      <c r="L52" s="4">
         <f>K52*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="5">
+        <v>0.76949999999999996</v>
+      </c>
+      <c r="M52" s="4">
         <f>L52*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="N52" s="6">
-        <v>0.95669999999999999</v>
-      </c>
-      <c r="O52" s="6">
-        <v>0.8993000000000001</v>
-      </c>
-      <c r="P52" s="6">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7">
+        <v>0.807975</v>
+      </c>
+      <c r="N52">
+        <v>0.93</v>
+      </c>
+      <c r="O52">
+        <f>N52*0.95</f>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P52">
+        <f>MIN(N52*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q52">
+        <v>0.72</v>
+      </c>
+      <c r="R52" s="4">
         <f>Q52*0.95</f>
-        <v>0</v>
-      </c>
-      <c r="S52" s="7">
+        <v>0.68399999999999994</v>
+      </c>
+      <c r="S52" s="4">
         <f>R52*1.05</f>
-        <v>0</v>
+        <v>0.71819999999999995</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
@@ -4721,7 +4732,7 @@
         <v>0.05</v>
       </c>
       <c r="J53" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F53:I53)</f>
         <v>1</v>
       </c>
       <c r="K53" s="10">
@@ -4759,73 +4770,65 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E54" t="s">
         <v>69</v>
       </c>
-      <c r="F54">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="G54">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="H54">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="I54">
-        <v>7.0999999999999994E-2</v>
+      <c r="F54" s="5">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5">
+        <v>0</v>
       </c>
       <c r="J54" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F54:I54)</f>
         <v>1</v>
       </c>
-      <c r="K54">
-        <v>0.87</v>
-      </c>
-      <c r="L54" s="4">
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5">
         <f>K54*0.95</f>
-        <v>0.82650000000000001</v>
-      </c>
-      <c r="M54" s="4">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5">
         <f>L54*1.05</f>
-        <v>0.86782500000000007</v>
-      </c>
-      <c r="N54">
-        <v>0.93</v>
-      </c>
-      <c r="O54">
-        <f>N54*0.95</f>
-        <v>0.88349999999999995</v>
-      </c>
-      <c r="P54">
-        <f>MIN(N54*1.05, 0.995)</f>
-        <v>0.97650000000000015</v>
-      </c>
-      <c r="Q54">
-        <v>0.61</v>
-      </c>
-      <c r="R54" s="4">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6">
+        <v>0.95669999999999999</v>
+      </c>
+      <c r="O54" s="6">
+        <v>0.8993000000000001</v>
+      </c>
+      <c r="P54" s="6">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
         <f>Q54*0.95</f>
-        <v>0.57950000000000002</v>
-      </c>
-      <c r="S54" s="4">
+        <v>0</v>
+      </c>
+      <c r="S54" s="7">
         <f>R54*1.05</f>
-        <v>0.60847499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B55" t="s">
         <v>73</v>
@@ -4840,19 +4843,19 @@
         <v>69</v>
       </c>
       <c r="F55">
-        <v>0.377</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="G55">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="H55">
-        <v>0.52800000000000002</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="I55">
-        <v>7.6999999999999999E-2</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="J55" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F55:I55)</f>
         <v>1</v>
       </c>
       <c r="K55">
@@ -4891,7 +4894,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
         <v>73</v>
@@ -4906,31 +4909,31 @@
         <v>69</v>
       </c>
       <c r="F56">
-        <v>2.9000000000000001E-2</v>
+        <v>0.377</v>
       </c>
       <c r="G56">
-        <v>7.0000000000000001E-3</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="H56">
-        <v>0.92500000000000004</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="I56">
-        <v>3.9E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="J56" s="9">
-        <f t="shared" si="0"/>
+        <f>SUM(F56:I56)</f>
         <v>1</v>
       </c>
       <c r="K56">
-        <v>0.84000000000000008</v>
+        <v>0.87</v>
       </c>
       <c r="L56" s="4">
         <f>K56*0.95</f>
-        <v>0.79800000000000004</v>
+        <v>0.82650000000000001</v>
       </c>
       <c r="M56" s="4">
         <f>L56*1.05</f>
-        <v>0.83790000000000009</v>
+        <v>0.86782500000000007</v>
       </c>
       <c r="N56">
         <v>0.93</v>
@@ -4944,26 +4947,26 @@
         <v>0.97650000000000015</v>
       </c>
       <c r="Q56">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R56" s="4">
         <f>Q56*0.95</f>
-        <v>0.66499999999999992</v>
+        <v>0.57950000000000002</v>
       </c>
       <c r="S56" s="4">
         <f>R56*1.05</f>
-        <v>0.69824999999999993</v>
+        <v>0.60847499999999999</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
         <v>69</v>
@@ -4971,335 +4974,401 @@
       <c r="E57" t="s">
         <v>69</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G57">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H57">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="I57">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J57" s="9">
+        <f>SUM(F57:I57)</f>
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="L57" s="4">
+        <f>K57*0.95</f>
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="M57" s="4">
+        <f>L57*1.05</f>
+        <v>0.83790000000000009</v>
+      </c>
+      <c r="N57">
+        <v>0.93</v>
+      </c>
+      <c r="O57">
+        <f>N57*0.95</f>
+        <v>0.88349999999999995</v>
+      </c>
+      <c r="P57">
+        <f>MIN(N57*1.05, 0.995)</f>
+        <v>0.97650000000000015</v>
+      </c>
+      <c r="Q57">
+        <v>0.7</v>
+      </c>
+      <c r="R57" s="4">
+        <f>Q57*0.95</f>
+        <v>0.66499999999999992</v>
+      </c>
+      <c r="S57" s="4">
+        <f>R57*1.05</f>
+        <v>0.69824999999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58" s="5">
         <f>AVERAGE('trash fish table'!F2:F6)</f>
         <v>0.56830740870546492</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G58" s="5">
         <f>AVERAGE('trash fish table'!G2:G6)</f>
         <v>0.2240987667741102</v>
       </c>
-      <c r="H57" s="5">
+      <c r="H58" s="5">
         <f>AVERAGE('trash fish table'!I2:I6)</f>
         <v>9.0773327441505319E-2</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I58" s="5">
         <f>AVERAGE('trash fish table'!H2:H6)</f>
         <v>0.11682049707891951</v>
       </c>
-      <c r="J57" s="9">
-        <f t="shared" si="0"/>
+      <c r="J58" s="9">
+        <f>SUM(F58:I58)</f>
         <v>1</v>
       </c>
-      <c r="K57" s="10">
+      <c r="K58" s="10">
         <v>0.87980000000000003</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L58" s="10">
         <v>0.82969999999999999</v>
       </c>
-      <c r="M57" s="10">
+      <c r="M58" s="10">
         <v>0.92209999999999992</v>
       </c>
-      <c r="N57" s="10">
+      <c r="N58" s="10">
         <v>0.95669999999999999</v>
       </c>
-      <c r="O57" s="10">
+      <c r="O58" s="10">
         <v>0.8993000000000001</v>
       </c>
-      <c r="P57" s="10">
+      <c r="P58" s="10">
         <v>0.99199999999999999</v>
       </c>
-      <c r="Q57" s="10">
+      <c r="Q58" s="10">
         <f>83.3/100</f>
         <v>0.83299999999999996</v>
       </c>
-      <c r="R57" s="10">
+      <c r="R58" s="10">
         <f>74.5/100</f>
         <v>0.745</v>
       </c>
-      <c r="S57" s="10">
+      <c r="S58" s="10">
         <f>92.6/100</f>
         <v>0.92599999999999993</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>31</v>
-      </c>
-      <c r="B58" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" t="s">
-        <v>68</v>
-      </c>
-      <c r="E58" t="s">
-        <v>69</v>
-      </c>
-      <c r="F58" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="G58" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="H58" s="7">
-        <f>1-SUM(F58:G58,I58)</f>
-        <v>0.83000000000000007</v>
-      </c>
-      <c r="I58" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="J58" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K58" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="L58" s="10">
-        <f>K58*0.94</f>
-        <v>0.84599999999999997</v>
-      </c>
-      <c r="M58" s="10">
-        <f>L58*1.06</f>
-        <v>0.89676</v>
-      </c>
-      <c r="N58" s="5">
-        <v>0.95176181599999998</v>
-      </c>
-      <c r="O58" s="5">
-        <f>N58*0.95</f>
-        <v>0.90417372519999994</v>
-      </c>
-      <c r="P58" s="5">
-        <f>N58*1.05</f>
-        <v>0.99934990680000002</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="R58" s="10">
-        <f>Q58*0.95</f>
-        <v>0.76</v>
-      </c>
-      <c r="S58" s="10">
-        <f>R58*1.05</f>
-        <v>0.79800000000000004</v>
-      </c>
-    </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
         <v>73</v>
       </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>68</v>
+      </c>
       <c r="E59" t="s">
         <v>69</v>
       </c>
-      <c r="F59">
-        <v>0.17299999999999999</v>
+      <c r="F59" s="5">
+        <v>0.13</v>
       </c>
       <c r="G59" s="5">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="H59" s="9">
-        <f>1-F59-G59-I59</f>
-        <v>0.73299999999999987</v>
+        <v>0.02</v>
+      </c>
+      <c r="H59" s="7">
+        <f>1-SUM(F59:G59,I59)</f>
+        <v>0.83000000000000007</v>
       </c>
       <c r="I59" s="5">
-        <v>5.6000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="J59" s="9">
-        <f t="shared" si="0"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="K59" s="9">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="N59">
-        <v>0.96</v>
-      </c>
-      <c r="Q59">
-        <v>0.57099999999999995</v>
+        <f>SUM(F59:I59)</f>
+        <v>1</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="L59" s="10">
+        <f>K59*0.94</f>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="M59" s="10">
+        <f>L59*1.06</f>
+        <v>0.89676</v>
+      </c>
+      <c r="N59" s="5">
+        <v>0.95176181599999998</v>
+      </c>
+      <c r="O59" s="5">
+        <f>N59*0.95</f>
+        <v>0.90417372519999994</v>
+      </c>
+      <c r="P59" s="5">
+        <f>N59*1.05</f>
+        <v>0.99934990680000002</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="R59" s="10">
+        <f>Q59*0.95</f>
+        <v>0.76</v>
+      </c>
+      <c r="S59" s="10">
+        <f>R59*1.05</f>
+        <v>0.79800000000000004</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
         <v>73</v>
       </c>
-      <c r="C60" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" t="s">
-        <v>68</v>
-      </c>
       <c r="E60" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G60" s="5">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="H60" s="9">
+        <f>1-F60-G60-I60</f>
+        <v>0.73299999999999987</v>
+      </c>
+      <c r="I60" s="5">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="J60" s="9">
+        <f>SUM(F60:I60)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="K60" s="9">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="N60">
+        <v>0.96</v>
+      </c>
+      <c r="Q60">
+        <v>0.57099999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="5">
         <f>766/1000</f>
         <v>0.76600000000000001</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G61" s="5">
         <f>74/1000</f>
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="H60" s="7">
-        <f>1-SUM(F60:G60,I60)</f>
+      <c r="H61" s="7">
+        <f>1-SUM(F61:G61,I61)</f>
         <v>0.15300000000000002</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I61" s="5">
         <f>7/1000</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J60" s="9">
-        <f t="shared" si="0"/>
+      <c r="J61" s="9">
+        <f>SUM(F61:I61)</f>
         <v>1</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K61" s="5">
         <v>0.89</v>
       </c>
-      <c r="L60" s="10">
-        <f>K60*0.94</f>
+      <c r="L61" s="10">
+        <f>K61*0.94</f>
         <v>0.83660000000000001</v>
       </c>
-      <c r="M60" s="10">
-        <f>L60*1.06</f>
+      <c r="M61" s="10">
+        <f>L61*1.06</f>
         <v>0.88679600000000003</v>
       </c>
-      <c r="N60" s="5">
+      <c r="N61" s="5">
         <v>0.95176181599999998</v>
       </c>
-      <c r="O60" s="5">
-        <f>N60*0.95</f>
+      <c r="O61" s="5">
+        <f>N61*0.95</f>
         <v>0.90417372519999994</v>
       </c>
-      <c r="P60" s="5">
-        <f>N60*1.05</f>
+      <c r="P61" s="5">
+        <f>N61*1.05</f>
         <v>0.99934990680000002</v>
       </c>
-      <c r="Q60" s="5">
+      <c r="Q61" s="5">
         <v>0.75</v>
       </c>
-      <c r="R60" s="10">
-        <f>Q60*0.95</f>
+      <c r="R61" s="10">
+        <f>Q61*0.95</f>
         <v>0.71249999999999991</v>
       </c>
-      <c r="S60" s="10">
-        <f>R60*1.05</f>
+      <c r="S61" s="10">
+        <f>R61*1.05</f>
         <v>0.74812499999999993</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>33</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>72</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>69</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>69</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E62" t="s">
         <v>69</v>
       </c>
-      <c r="F61">
+      <c r="F62">
         <v>0.48</v>
       </c>
-      <c r="G61">
+      <c r="G62">
         <v>0.04</v>
       </c>
-      <c r="H61">
+      <c r="H62">
         <v>0.41</v>
       </c>
-      <c r="I61">
+      <c r="I62">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J61" s="9">
-        <f t="shared" si="0"/>
+      <c r="J62" s="9">
+        <f>SUM(F62:I62)</f>
         <v>1</v>
       </c>
-      <c r="K61">
+      <c r="K62">
         <v>0.82000000000000006</v>
       </c>
-      <c r="L61" s="4">
-        <f>K61*0.95</f>
+      <c r="L62" s="4">
+        <f>K62*0.95</f>
         <v>0.77900000000000003</v>
       </c>
-      <c r="M61" s="4">
-        <f>L61*1.05</f>
+      <c r="M62" s="4">
+        <f>L62*1.05</f>
         <v>0.81795000000000007</v>
       </c>
-      <c r="N61">
+      <c r="N62">
         <v>0.93</v>
       </c>
-      <c r="O61">
-        <f>N61*0.95</f>
+      <c r="O62">
+        <f>N62*0.95</f>
         <v>0.88349999999999995</v>
       </c>
-      <c r="P61">
-        <f>MIN(N61*1.05, 0.995)</f>
+      <c r="P62">
+        <f>MIN(N62*1.05, 0.995)</f>
         <v>0.97650000000000015</v>
       </c>
-      <c r="Q61">
+      <c r="Q62">
         <v>0.7</v>
       </c>
-      <c r="R61" s="4">
-        <f>Q61*0.95</f>
+      <c r="R62" s="4">
+        <f>Q62*0.95</f>
         <v>0.66499999999999992</v>
       </c>
-      <c r="S61" s="4">
-        <f>R61*1.05</f>
+      <c r="S62" s="4">
+        <f>R62*1.05</f>
         <v>0.69824999999999993</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S61" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S61">
-      <sortCondition ref="A1:A61"/>
+  <autoFilter ref="A1:S62" xr:uid="{FEB86C80-6855-4296-9746-1E92B0D65FFA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S62">
+      <sortCondition ref="A1:A62"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="K2:S42">
+  <conditionalFormatting sqref="K2:S43">
     <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K54:S55">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+  <conditionalFormatting sqref="K53:S53">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K57:S57">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="K55:S56">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L56:M56">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
+  <conditionalFormatting sqref="K58:S58">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O56:P56">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+  <conditionalFormatting sqref="L57:M57">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R56:S56">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="O57:P57">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K52:S52">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="R57:S57">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
